--- a/data/trans_orig/P36BPD07_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD07_2023-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el número de bebidas carbonatadas y/o azucaradas que consume al día en 2023</t>
+          <t>Población según el número de bebidas carbonatadas y/o azucaradas que consume al día en 2023 (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>38462</t>
+          <t>39657</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>78774</t>
+          <t>80141</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>24710</t>
+          <t>24452</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>51252</t>
+          <t>51155</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>69258</t>
+          <t>70009</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>116939</t>
+          <t>118980</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,79%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>232669</t>
+          <t>231302</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>272981</t>
+          <t>271786</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>74,71%</t>
+          <t>74,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,65%</t>
+          <t>87,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>238383</t>
+          <t>238480</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>264925</t>
+          <t>265183</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,3%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>484138</t>
+          <t>482097</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>531819</t>
+          <t>531068</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,55%</t>
+          <t>80,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>88,35%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>84525</t>
+          <t>83118</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>134442</t>
+          <t>131298</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>79752</t>
+          <t>81169</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>114093</t>
+          <t>114705</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>173835</t>
+          <t>174055</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>233037</t>
+          <t>233466</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,63%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>383948</t>
+          <t>387092</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>433865</t>
+          <t>435272</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,07%</t>
+          <t>74,67%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,69%</t>
+          <t>83,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>399284</t>
+          <t>398672</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>433625</t>
+          <t>432208</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,78%</t>
+          <t>77,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,47%</t>
+          <t>84,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>798730</t>
+          <t>798301</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>857932</t>
+          <t>857712</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,41%</t>
+          <t>77,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,15%</t>
+          <t>83,13%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>45987</t>
+          <t>45373</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>74105</t>
+          <t>75411</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>31586</t>
+          <t>31392</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>52856</t>
+          <t>52588</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>84360</t>
+          <t>84513</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>119774</t>
+          <t>118429</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>17,84%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>241108</t>
+          <t>239802</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>269226</t>
+          <t>269840</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,49%</t>
+          <t>76,08%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,41%</t>
+          <t>85,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>295590</t>
+          <t>295858</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>316860</t>
+          <t>317054</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>90,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>543885</t>
+          <t>545230</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>579299</t>
+          <t>579146</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,95%</t>
+          <t>82,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>87,27%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>35960</t>
+          <t>36171</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>71006</t>
+          <t>73438</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30728</t>
+          <t>32894</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>74632</t>
+          <t>77086</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>77864</t>
+          <t>75910</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>135902</t>
+          <t>136230</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,3%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>241551</t>
+          <t>239119</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>276597</t>
+          <t>276386</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,28%</t>
+          <t>76,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>88,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>400047</t>
+          <t>397593</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>443951</t>
+          <t>441785</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,28%</t>
+          <t>83,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>651334</t>
+          <t>651006</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>709372</t>
+          <t>711326</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,74%</t>
+          <t>82,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>90,36%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>32277</t>
+          <t>31711</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>53069</t>
+          <t>52568</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19207</t>
+          <t>18506</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>33312</t>
+          <t>32895</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>54085</t>
+          <t>54223</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>78506</t>
+          <t>80072</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,69%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>125673</t>
+          <t>126174</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>146465</t>
+          <t>147031</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>70,31%</t>
+          <t>70,59%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>81,94%</t>
+          <t>82,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>174962</t>
+          <t>175379</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>189067</t>
+          <t>189768</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,01%</t>
+          <t>84,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>91,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>308510</t>
+          <t>306944</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>332931</t>
+          <t>332793</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>79,72%</t>
+          <t>79,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>85,99%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>28666</t>
+          <t>29072</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>52274</t>
+          <t>51619</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12680</t>
+          <t>12675</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>27151</t>
+          <t>27138</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>45289</t>
+          <t>44766</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>71213</t>
+          <t>70538</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,39%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>217362</t>
+          <t>218017</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>240970</t>
+          <t>240564</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>80,61%</t>
+          <t>80,86%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>89,22%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>229905</t>
+          <t>229918</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>244376</t>
+          <t>244381</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>455479</t>
+          <t>456154</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>481403</t>
+          <t>481926</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>86,61%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,5%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>104512</t>
+          <t>103290</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>160774</t>
+          <t>159230</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>50976</t>
+          <t>53906</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>161910</t>
+          <t>163881</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>136057</t>
+          <t>148540</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>299942</t>
+          <t>298204</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,29%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>460597</t>
+          <t>462141</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>516859</t>
+          <t>518081</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>74,13%</t>
+          <t>74,37%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>83,18%</t>
+          <t>83,38%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>686459</t>
+          <t>684488</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>797393</t>
+          <t>794463</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>80,92%</t>
+          <t>80,68%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1169798</t>
+          <t>1171536</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1333683</t>
+          <t>1321200</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>79,59%</t>
+          <t>79,71%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>89,89%</t>
         </is>
       </c>
     </row>
@@ -3131,12 +3131,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>190679</t>
+          <t>198665</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>579652</t>
+          <t>584420</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,12 +3146,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>62,49%</t>
+          <t>63,0%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>361624</t>
+          <t>356997</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>406272</t>
+          <t>406886</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>50,47%</t>
+          <t>49,83%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>56,71%</t>
+          <t>56,79%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>489400</t>
+          <t>465321</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>953761</t>
+          <t>957874</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>58,01%</t>
+          <t>58,26%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>347972</t>
+          <t>343204</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>736945</t>
+          <t>728959</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>37,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>79,44%</t>
+          <t>78,58%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>310187</t>
+          <t>309573</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>354835</t>
+          <t>359462</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>43,29%</t>
+          <t>43,21%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>49,53%</t>
+          <t>50,17%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>690323</t>
+          <t>686210</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1154684</t>
+          <t>1178763</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>41,99%</t>
+          <t>41,74%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>70,23%</t>
+          <t>71,7%</t>
         </is>
       </c>
     </row>
@@ -3474,12 +3474,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>709792</t>
+          <t>698607</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>995730</t>
+          <t>992630</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>630700</t>
+          <t>636025</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>837814</t>
+          <t>843235</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,17 +3539,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1672793</t>
+          <t>1672794</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1444774</t>
+          <t>1456891</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1804471</t>
+          <t>1803512</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3559,12 +3559,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>25,36%</t>
         </is>
       </c>
     </row>
@@ -3587,12 +3587,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2459246</t>
+          <t>2462346</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2745184</t>
+          <t>2756369</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>71,18%</t>
+          <t>71,27%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>79,46%</t>
+          <t>79,78%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2818481</t>
+          <t>2813060</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3025595</t>
+          <t>3020270</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>77,09%</t>
+          <t>76,94%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>82,75%</t>
+          <t>82,6%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5306799</t>
+          <t>5307759</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5666496</t>
+          <t>5654380</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3672,12 +3672,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>74,63%</t>
+          <t>74,64%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>79,68%</t>
+          <t>79,51%</t>
         </is>
       </c>
     </row>
@@ -3765,17 +3765,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7111270</t>
+          <t>7111271</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7111270</t>
+          <t>7111271</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7111270</t>
+          <t>7111271</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">

--- a/data/trans_orig/P36BPD07_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD07_2023-Provincia-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>55695</t>
+          <t>54493</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>39657</t>
+          <t>40746</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>80141</t>
+          <t>70580</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>35230</t>
+          <t>44747</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>24452</t>
+          <t>34410</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>51155</t>
+          <t>60012</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>90925</t>
+          <t>99240</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>70009</t>
+          <t>81832</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>118980</t>
+          <t>121021</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,06%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>255748</t>
+          <t>264352</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>231302</t>
+          <t>248265</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>271786</t>
+          <t>278099</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>82,91%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>74,27%</t>
+          <t>77,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>87,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>254405</t>
+          <t>271314</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>238480</t>
+          <t>256049</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>265183</t>
+          <t>281651</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>85,84%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>81,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>89,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>510152</t>
+          <t>535666</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>482097</t>
+          <t>513885</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>531068</t>
+          <t>553074</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>84,37%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,21%</t>
+          <t>80,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>87,11%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>106112</t>
+          <t>106453</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>83118</t>
+          <t>84961</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>131298</t>
+          <t>133164</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>96301</t>
+          <t>101690</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>81169</t>
+          <t>86577</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>114705</t>
+          <t>121230</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>202414</t>
+          <t>208143</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>174055</t>
+          <t>179871</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>233466</t>
+          <t>238723</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,19%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>412278</t>
+          <t>424194</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>387092</t>
+          <t>397483</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>435272</t>
+          <t>445686</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>79,53%</t>
+          <t>79,94%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,67%</t>
+          <t>74,91%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,97%</t>
+          <t>83,99%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>417076</t>
+          <t>443265</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>398672</t>
+          <t>423725</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>432208</t>
+          <t>458378</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>81,24%</t>
+          <t>81,34%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,66%</t>
+          <t>77,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,19%</t>
+          <t>84,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>829353</t>
+          <t>867459</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>798301</t>
+          <t>836879</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>857712</t>
+          <t>895731</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>80,38%</t>
+          <t>80,65%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,37%</t>
+          <t>77,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,13%</t>
+          <t>83,28%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>513377</t>
+          <t>544955</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>513377</t>
+          <t>544955</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>513377</t>
+          <t>544955</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1031767</t>
+          <t>1075602</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1031767</t>
+          <t>1075602</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1031767</t>
+          <t>1075602</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>59292</t>
+          <t>62092</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>45373</t>
+          <t>48949</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>75411</t>
+          <t>77137</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,17 +1446,17 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>40920</t>
+          <t>41772</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>31392</t>
+          <t>32549</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>52588</t>
+          <t>53685</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>100212</t>
+          <t>103865</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>84513</t>
+          <t>87716</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>118429</t>
+          <t>122797</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>18,31%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>255921</t>
+          <t>253037</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>239802</t>
+          <t>237992</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>269840</t>
+          <t>266180</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>81,19%</t>
+          <t>80,3%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,08%</t>
+          <t>75,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,61%</t>
+          <t>84,47%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,17 +1559,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>307526</t>
+          <t>313927</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>295858</t>
+          <t>302014</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>317054</t>
+          <t>323150</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>563447</t>
+          <t>566962</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>545230</t>
+          <t>548030</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>579146</t>
+          <t>583111</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>84,9%</t>
+          <t>84,52%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,16%</t>
+          <t>81,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>86,92%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>315213</t>
+          <t>315129</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>315213</t>
+          <t>315129</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>315213</t>
+          <t>315129</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>348446</t>
+          <t>355699</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>348446</t>
+          <t>355699</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>348446</t>
+          <t>355699</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>663659</t>
+          <t>670827</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>663659</t>
+          <t>670827</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>663659</t>
+          <t>670827</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>52558</t>
+          <t>63821</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36171</t>
+          <t>47190</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>73438</t>
+          <t>87403</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>54788</t>
+          <t>64315</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>32894</t>
+          <t>48781</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>77086</t>
+          <t>80963</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>107346</t>
+          <t>128136</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>75910</t>
+          <t>103660</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>136230</t>
+          <t>156025</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>19,65%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>259999</t>
+          <t>309324</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>239119</t>
+          <t>285742</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>276386</t>
+          <t>325955</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>83,18%</t>
+          <t>82,9%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,5%</t>
+          <t>76,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,43%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>419891</t>
+          <t>356542</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>397593</t>
+          <t>339894</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>441785</t>
+          <t>372076</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>84,72%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>80,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>88,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>679890</t>
+          <t>665866</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>651006</t>
+          <t>637977</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>711326</t>
+          <t>690342</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>83,86%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,7%</t>
+          <t>80,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>86,94%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>474679</t>
+          <t>420857</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>474679</t>
+          <t>420857</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>474679</t>
+          <t>420857</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>787236</t>
+          <t>794002</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>787236</t>
+          <t>794002</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>787236</t>
+          <t>794002</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>41348</t>
+          <t>48607</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>31711</t>
+          <t>39157</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>52568</t>
+          <t>62172</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>30,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>24696</t>
+          <t>29083</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18506</t>
+          <t>21619</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32895</t>
+          <t>37715</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>66044</t>
+          <t>77690</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>54223</t>
+          <t>64264</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>80072</t>
+          <t>91084</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>21,06%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>137394</t>
+          <t>157058</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>126174</t>
+          <t>143493</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>147031</t>
+          <t>166508</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>76,87%</t>
+          <t>76,37%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>70,59%</t>
+          <t>69,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,26%</t>
+          <t>80,96%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>183578</t>
+          <t>197740</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>175379</t>
+          <t>189108</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>189768</t>
+          <t>205204</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>87,18%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>83,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>90,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>320972</t>
+          <t>354798</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>306944</t>
+          <t>341404</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>332793</t>
+          <t>368224</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>82,94%</t>
+          <t>82,04%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>79,31%</t>
+          <t>78,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,99%</t>
+          <t>85,14%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>38723</t>
+          <t>38591</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>29072</t>
+          <t>29001</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>51619</t>
+          <t>50272</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>18409</t>
+          <t>19083</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12675</t>
+          <t>13367</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>27138</t>
+          <t>26797</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>57132</t>
+          <t>57674</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>44766</t>
+          <t>46263</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>70538</t>
+          <t>71856</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,44%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>230913</t>
+          <t>232116</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>218017</t>
+          <t>220435</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>240564</t>
+          <t>241706</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>85,64%</t>
+          <t>85,74%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>80,86%</t>
+          <t>81,43%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>89,29%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>238647</t>
+          <t>244667</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>229918</t>
+          <t>236953</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>244381</t>
+          <t>250383</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>89,84%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>469560</t>
+          <t>476783</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>456154</t>
+          <t>462601</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>481926</t>
+          <t>488194</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>86,56%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>91,34%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>129144</t>
+          <t>139191</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>103290</t>
+          <t>115119</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>159230</t>
+          <t>166066</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>117346</t>
+          <t>144488</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>53906</t>
+          <t>122442</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>163881</t>
+          <t>167290</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>246490</t>
+          <t>283678</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>148540</t>
+          <t>251001</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>298204</t>
+          <t>321766</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>21,65%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>492227</t>
+          <t>577405</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>462141</t>
+          <t>550530</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>518081</t>
+          <t>601477</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>79,22%</t>
+          <t>80,58%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>74,37%</t>
+          <t>76,83%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>83,38%</t>
+          <t>83,94%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>731023</t>
+          <t>625411</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>684488</t>
+          <t>602609</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>794463</t>
+          <t>647457</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>86,17%</t>
+          <t>81,23%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>78,27%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>84,1%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1223250</t>
+          <t>1202817</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1171536</t>
+          <t>1164729</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1321200</t>
+          <t>1235494</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>83,23%</t>
+          <t>80,92%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>79,71%</t>
+          <t>78,35%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>83,11%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>621371</t>
+          <t>716596</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>621371</t>
+          <t>716596</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>621371</t>
+          <t>716596</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>848369</t>
+          <t>769899</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>848369</t>
+          <t>769899</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>848369</t>
+          <t>769899</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1469740</t>
+          <t>1486495</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1469740</t>
+          <t>1486495</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1469740</t>
+          <t>1486495</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3126,32 +3126,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>419926</t>
+          <t>493355</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>198665</t>
+          <t>461043</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>584420</t>
+          <t>520372</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>45,27%</t>
+          <t>61,91%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>57,86%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>63,0%</t>
+          <t>65,3%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,32 +3161,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>382304</t>
+          <t>438379</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>356997</t>
+          <t>408336</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>406886</t>
+          <t>462725</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>53,36%</t>
+          <t>52,82%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>49,83%</t>
+          <t>49,2%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>56,79%</t>
+          <t>55,75%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>802231</t>
+          <t>931735</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>465321</t>
+          <t>892958</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>957874</t>
+          <t>968803</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>48,8%</t>
+          <t>57,27%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>54,89%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>58,26%</t>
+          <t>59,55%</t>
         </is>
       </c>
     </row>
@@ -3239,32 +3239,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>507698</t>
+          <t>303518</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>343204</t>
+          <t>276501</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>728959</t>
+          <t>335830</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>54,73%</t>
+          <t>38,09%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>37,0%</t>
+          <t>34,7%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>78,58%</t>
+          <t>42,14%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,32 +3274,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>334155</t>
+          <t>391555</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>309573</t>
+          <t>367209</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>359462</t>
+          <t>421598</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>46,64%</t>
+          <t>47,18%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>43,21%</t>
+          <t>44,25%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>50,17%</t>
+          <t>50,8%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>841853</t>
+          <t>695072</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>686210</t>
+          <t>658004</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1178763</t>
+          <t>733849</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
+          <t>42,73%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>41,74%</t>
+          <t>40,45%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>71,7%</t>
+          <t>45,11%</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>927624</t>
+          <t>796873</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>927624</t>
+          <t>796873</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>927624</t>
+          <t>796873</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>716459</t>
+          <t>829934</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>716459</t>
+          <t>829934</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>716459</t>
+          <t>829934</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1644084</t>
+          <t>1626807</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1644084</t>
+          <t>1626807</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1644084</t>
+          <t>1626807</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3469,32 +3469,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>902799</t>
+          <t>1006603</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>698607</t>
+          <t>943775</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>992630</t>
+          <t>1067488</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,32 +3504,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>769995</t>
+          <t>883558</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>636025</t>
+          <t>833195</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>843235</t>
+          <t>933759</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1672794</t>
+          <t>1890161</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1456891</t>
+          <t>1808856</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1803512</t>
+          <t>1967680</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>27,12%</t>
         </is>
       </c>
     </row>
@@ -3582,32 +3582,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2552177</t>
+          <t>2521004</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2462346</t>
+          <t>2460119</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2756369</t>
+          <t>2583832</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>73,87%</t>
+          <t>71,46%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>71,27%</t>
+          <t>69,74%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>79,78%</t>
+          <t>73,25%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,32 +3617,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2886300</t>
+          <t>2844420</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2813060</t>
+          <t>2794219</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3020270</t>
+          <t>2894783</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>78,94%</t>
+          <t>76,3%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>76,94%</t>
+          <t>74,95%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>82,6%</t>
+          <t>77,65%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,32 +3652,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>5438477</t>
+          <t>5365424</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5307759</t>
+          <t>5287905</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5654380</t>
+          <t>5446729</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>76,48%</t>
+          <t>73,95%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>74,64%</t>
+          <t>72,88%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>79,51%</t>
+          <t>75,07%</t>
         </is>
       </c>
     </row>
@@ -3695,17 +3695,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3454976</t>
+          <t>3527607</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3454976</t>
+          <t>3527607</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3454976</t>
+          <t>3527607</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3730,17 +3730,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3656295</t>
+          <t>3727978</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3656295</t>
+          <t>3727978</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3656295</t>
+          <t>3727978</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7111271</t>
+          <t>7255585</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7111271</t>
+          <t>7255585</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7111271</t>
+          <t>7255585</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
